--- a/assets/templates/master/TESA_Master_Pre_Primary.xlsx
+++ b/assets/templates/master/TESA_Master_Pre_Primary.xlsx
@@ -622,7 +622,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -653,27 +657,33 @@
         <v>Blood Group</v>
       </c>
       <c r="J1" t="str">
+        <v>Height (cm)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Weight (kg)</v>
+      </c>
+      <c r="L1" t="str">
         <v>Address</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Photo URL</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>Teacher Rating</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>Behaviour Points</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>Previous Term %</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>Conduct</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>Achievement</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -705,28 +715,34 @@
       <c r="I2" t="str">
         <v>B+</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J2">
+        <v>98</v>
+      </c>
+      <c r="K2">
+        <v>15.2</v>
+      </c>
+      <c r="L2" t="str">
         <v>Ichalkaranji</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v/>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>8</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>9</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>72</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>Excellent</v>
       </c>
-      <c r="P2" t="str">
+      <c r="R2" t="str">
         <v/>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>example row - replace</v>
       </c>
     </row>
@@ -758,35 +774,40 @@
       <c r="I3" t="str">
         <v>O+</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J3">
+        <v>103</v>
+      </c>
+      <c r="K3">
+        <v>16.8</v>
+      </c>
+      <c r="L3" t="str">
         <v>Ichalkaranji</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v>6</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>7</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>61</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <v>Very Good</v>
       </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
         <v/>
       </c>
-      <c r="Q3" t="str">
+      <c r="S3" t="str">
         <v>example row - replace</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1810,13 +1831,6 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E8"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="52.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/assets/templates/master/TESA_Master_Pre_Primary.xlsx
+++ b/assets/templates/master/TESA_Master_Pre_Primary.xlsx
@@ -405,217 +405,216 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:B41"/>
+  <dimension ref="A1:A41"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="str">
+      <c r="A1" t="str">
         <v>Pre-Primary Master Workbook</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="str">
+      <c r="A2" t="str">
         <v>Everything for one kindergarten class in a single file</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="str">
+      <c r="A3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="str">
+      <c r="A4" t="str">
         <v>One file. Every tool.</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="str">
+      <c r="A5" t="str">
         <v>Fill this workbook once and the same file drives the progress dashboard AND every front-office tool.</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="str">
+      <c r="A6" t="str">
         <v>You never type the same student name into two places.</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="str">
+      <c r="A7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="str">
+      <c r="A8" t="str">
         <v>The sheets in this workbook</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="str">
+      <c r="A9" t="str">
         <v>Students     - the roster. Every tool reads this.</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="str">
+      <c r="A10" t="str">
         <v>Evaluation   - one block of columns per term: a rating and a comment for each development area.</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="str">
+      <c r="A11" t="str">
         <v>Attendance   - one dated column per class day.</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="str">
+      <c r="A12" t="str">
         <v>Charges / Payments - the fee ledger.</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="str">
+      <c r="A13" t="str">
         <v>Timetable    - one row per period.</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="str">
+      <c r="A14" t="str">
         <v>Notes        - dated observations about a child.</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="str">
+      <c r="A15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="str">
+      <c r="A16" t="str">
         <v>Which tool reads what</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="str">
+      <c r="A17" t="str">
         <v>Progress dashboard   -&gt;  Students, the academic sheet, Attendance</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="str">
+      <c r="A18" t="str">
         <v>Fees and Dues        -&gt;  Students, Charges, Payments</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="str">
+      <c r="A19" t="str">
         <v>ID Cards             -&gt;  Students (Photo URL, Blood Group, Address)</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="str">
+      <c r="A20" t="str">
         <v>Certificates         -&gt;  Students (Date of Birth, Admission Date, Conduct, Gender)</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="str">
+      <c r="A21" t="str">
         <v>Timetable            -&gt;  Timetable</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="str">
+      <c r="A22" t="str">
         <v>At-Risk Radar        -&gt;  the academic sheet, Attendance, Charges, Payments</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="str">
+      <c r="A23" t="str">
         <v>Parent File          -&gt;  the academic sheet (with TOPICS), Attendance, Notes</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="str">
+      <c r="A24" t="str">
         <v>Student File         -&gt;  Students, Charges, Payments</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="str">
+      <c r="A25" t="str">
         <v>Results Pack         -&gt;  the academic sheet, Students (Photo URL)</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="str">
+      <c r="A26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="str">
+      <c r="A27" t="str">
         <v>Rules that keep everything working</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="str">
+      <c r="A28" t="str">
         <v>Spell each student's name the SAME way on every sheet. That is how rows are matched together.</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="str">
+      <c r="A29" t="str">
         <v>Keep the header cell that says  Student Name  on every sheet.</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="str">
+      <c r="A30" t="str">
         <v>Do not leave blank rows between students.</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="str">
+      <c r="A31" t="str">
         <v>Delete any sheet you do not use - nothing breaks. Tools simply skip what is missing.</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="str">
+      <c r="A32" t="str">
         <v>Amounts are plain numbers: no rupee sign, no commas. Dates work as 2025-07-15 or 15-Jul-2025.</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="str">
+      <c r="A33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="str">
+      <c r="A34" t="str">
         <v>Where the report text comes from</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="str">
+      <c r="A35" t="str">
         <v>Teachers Note (on the academic sheet) is printed as the single note section on each report.</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="str">
-        <v>The Notes column on Students is used only if that is blank, and the Notes sheet keeps the dated history.</v>
+      <c r="A36" t="str">
+        <v>The Notes column on Students is used only if that is blank, and the Notes sheet prints as a dated timeline on the report.</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="str">
+      <c r="A37" t="str">
         <v>Practice suggestions are generated automatically underneath it - you do not type those.</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="str">
+      <c r="A38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="str">
+      <c r="A39" t="str">
         <v>The TOPICS row is the one worth filling</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="str">
+      <c r="A40" t="str">
         <v>Naming the chapter each column tested is what unlocks the personalised study plan in the Parent File,</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="str">
+      <c r="A41" t="str">
         <v>and topic-level strengths on reports. It is the single highest-value row in this workbook.</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="B1:B41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -623,10 +622,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S3"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1745,7 +1740,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="62.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1763,6 +1766,9 @@
       <c r="E1" t="str">
         <v>Note</v>
       </c>
+      <c r="F1" t="str">
+        <v>Share on report</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1780,6 +1786,9 @@
       <c r="E2" t="str">
         <v>Asked excellent questions in class this week - clearly reading ahead.</v>
       </c>
+      <c r="F2" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1797,6 +1806,9 @@
       <c r="E3" t="str">
         <v>Spoke to father about missed classes; he will send Rahul regularly from Monday.</v>
       </c>
+      <c r="F3" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1814,16 +1826,38 @@
       <c r="E4" t="str">
         <v>Handwriting has improved noticeably since the last test.</v>
       </c>
+      <c r="F4" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2025-08-14</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rahul Example</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Prof. Example</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Fee delay discussed with the office - staff record only.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>No</v>
+      </c>
     </row>
     <row r="7">
-      <c r="H7" t="str">
-        <v>A dated log. Add a row whenever something is worth remembering - it keeps the history a single Notes column cannot.</v>
+      <c r="G7" t="str">
+        <v>These dated notes now print on the student's report, newest first. Put No in "Share on report" to keep a row off it.</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
